--- a/act.xlsx
+++ b/act.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ylwgg\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D559DFE1-5016-44B0-8114-F85A0D1172A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A206D3-64FA-426F-9614-6DFB8F5B5FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15943" tabRatio="460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3328,9 +3328,6 @@
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
-    <t>跳转至默认页</t>
-  </si>
-  <si>
     <t>付款方式(0:不限 其他:银行名称-卡片类型)</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
@@ -3364,6 +3361,10 @@
   </si>
   <si>
     <t>C:\Users\ylwgg\Desktop\123.jpg</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>跳转至小程序</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
@@ -3980,18 +3981,60 @@
     <xf numFmtId="0" fontId="21" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4009,48 +4052,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4916,7 +4917,7 @@
         <v>22</v>
       </c>
       <c r="S1" s="40" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="T1" s="41" t="s">
         <v>99</v>
@@ -5019,7 +5020,7 @@
         <v>1719990431</v>
       </c>
       <c r="B3" s="56" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C3" s="57">
         <v>1.88</v>
@@ -5028,7 +5029,7 @@
         <v>1.89</v>
       </c>
       <c r="E3" s="58" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F3" s="55" t="s">
         <v>215</v>
@@ -5058,12 +5059,12 @@
         <v>221</v>
       </c>
       <c r="O3" s="58" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P3" s="60"/>
       <c r="Q3" s="60"/>
-      <c r="R3" s="55" t="s">
-        <v>222</v>
+      <c r="R3" s="56" t="s">
+        <v>231</v>
       </c>
       <c r="S3" s="62" t="s">
         <v>188</v>
@@ -5114,8 +5115,8 @@
       <formula1>5</formula1>
       <formula2>10000000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R3" xr:uid="{B030F964-F1BA-48C7-B351-FB06FCF2BDBC}">
-      <formula1>"跳转至默认页"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1:R1048576" xr:uid="{B030F964-F1BA-48C7-B351-FB06FCF2BDBC}">
+      <formula1>"跳转至默认页,跳转至付款码,跳转至小程序"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V3" xr:uid="{02B7E657-2D70-4A06-AC5B-3BF997A6E884}">
       <formula1>"该优惠不可以和本商户号创建的其他券同时使用（但可以享受立减和折扣）,该优惠可以和其他优惠同时使用."</formula1>
@@ -5133,126 +5134,126 @@
   <sheetFormatPr defaultRowHeight="14.15"/>
   <sheetData>
     <row r="1" spans="1:33" ht="26.15">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="82"/>
-      <c r="P1" s="82"/>
-      <c r="Q1" s="82"/>
-      <c r="R1" s="82"/>
-      <c r="S1" s="82"/>
-      <c r="T1" s="82"/>
-      <c r="U1" s="82"/>
-      <c r="V1" s="82"/>
-      <c r="W1" s="82"/>
-      <c r="X1" s="82"/>
-      <c r="Y1" s="82"/>
-      <c r="Z1" s="82"/>
-      <c r="AA1" s="82"/>
-      <c r="AB1" s="82"/>
-      <c r="AC1" s="82"/>
-      <c r="AD1" s="82"/>
-      <c r="AE1" s="82"/>
-      <c r="AF1" s="82"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
+      <c r="P1" s="72"/>
+      <c r="Q1" s="72"/>
+      <c r="R1" s="72"/>
+      <c r="S1" s="72"/>
+      <c r="T1" s="72"/>
+      <c r="U1" s="72"/>
+      <c r="V1" s="72"/>
+      <c r="W1" s="72"/>
+      <c r="X1" s="72"/>
+      <c r="Y1" s="72"/>
+      <c r="Z1" s="72"/>
+      <c r="AA1" s="72"/>
+      <c r="AB1" s="72"/>
+      <c r="AC1" s="72"/>
+      <c r="AD1" s="72"/>
+      <c r="AE1" s="72"/>
+      <c r="AF1" s="72"/>
       <c r="AG1" s="28"/>
     </row>
     <row r="2" spans="1:33">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="80" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="90" t="s">
+      <c r="B2" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="90" t="s">
+      <c r="C2" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="71" t="s">
+      <c r="D2" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="71" t="s">
+      <c r="E2" s="80" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="90" t="s">
+      <c r="F2" s="82" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="83" t="s">
+      <c r="G2" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="85"/>
-      <c r="L2" s="92" t="s">
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="71" t="s">
+      <c r="M2" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="92" t="s">
+      <c r="N2" s="84" t="s">
         <v>46</v>
       </c>
-      <c r="O2" s="92" t="s">
+      <c r="O2" s="84" t="s">
         <v>47</v>
       </c>
-      <c r="P2" s="86" t="s">
+      <c r="P2" s="76" t="s">
         <v>48</v>
       </c>
-      <c r="Q2" s="86"/>
-      <c r="R2" s="86"/>
-      <c r="S2" s="86"/>
-      <c r="T2" s="87" t="s">
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
-      <c r="W2" s="88"/>
-      <c r="X2" s="88"/>
-      <c r="Y2" s="89"/>
-      <c r="Z2" s="79" t="s">
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
+      <c r="W2" s="78"/>
+      <c r="X2" s="78"/>
+      <c r="Y2" s="79"/>
+      <c r="Z2" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="AA2" s="79" t="s">
+      <c r="AA2" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="AB2" s="71" t="s">
+      <c r="AB2" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="AC2" s="71" t="s">
+      <c r="AC2" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="AD2" s="73" t="s">
+      <c r="AD2" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="AE2" s="75" t="s">
+      <c r="AE2" s="89" t="s">
         <v>52</v>
       </c>
-      <c r="AF2" s="77" t="s">
+      <c r="AF2" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="AG2" s="69" t="s">
+      <c r="AG2" s="85" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:33" ht="27.45">
-      <c r="A3" s="72"/>
-      <c r="B3" s="91"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="91"/>
+      <c r="A3" s="81"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="83"/>
       <c r="G3" s="29" t="s">
         <v>18</v>
       </c>
@@ -5268,10 +5269,10 @@
       <c r="K3" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="92"/>
-      <c r="M3" s="91"/>
-      <c r="N3" s="92"/>
-      <c r="O3" s="92"/>
+      <c r="L3" s="84"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="84"/>
+      <c r="O3" s="84"/>
       <c r="P3" s="30" t="s">
         <v>55</v>
       </c>
@@ -5302,14 +5303,14 @@
       <c r="Y3" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
-      <c r="AB3" s="72"/>
-      <c r="AC3" s="72"/>
-      <c r="AD3" s="74"/>
-      <c r="AE3" s="76"/>
-      <c r="AF3" s="78"/>
-      <c r="AG3" s="70"/>
+      <c r="Z3" s="70"/>
+      <c r="AA3" s="70"/>
+      <c r="AB3" s="81"/>
+      <c r="AC3" s="81"/>
+      <c r="AD3" s="88"/>
+      <c r="AE3" s="90"/>
+      <c r="AF3" s="92"/>
+      <c r="AG3" s="86"/>
     </row>
     <row r="4" spans="1:33" ht="409.6">
       <c r="A4" s="13" t="s">
@@ -5412,6 +5413,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AF2:AF3"/>
     <mergeCell ref="AA2:AA3"/>
     <mergeCell ref="A1:AF1"/>
     <mergeCell ref="G2:K2"/>
@@ -5428,12 +5435,6 @@
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="O2:O3"/>
     <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AF2:AF3"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5564,7 +5565,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="66" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C3" s="66" t="s">
         <v>191</v>
@@ -5582,7 +5583,7 @@
         <v>2</v>
       </c>
       <c r="H3" s="66" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I3" s="58">
         <v>1</v>
@@ -5750,7 +5751,7 @@
     </row>
     <row r="3" spans="1:18" ht="409.6">
       <c r="A3" s="43" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B3" s="48">
         <v>20</v>
@@ -5759,7 +5760,7 @@
         <v>200</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E3" s="45">
         <v>9</v>
@@ -5933,7 +5934,7 @@
     </row>
     <row r="3" spans="1:18" ht="409.6">
       <c r="A3" s="53" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B3" s="43" t="s">
         <v>168</v>
@@ -5942,7 +5943,7 @@
         <v>11</v>
       </c>
       <c r="D3" s="53" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E3" s="50" t="s">
         <v>169</v>
